--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB QUART GRUES CRUZ.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB QUART GRUES CRUZ.xlsx
@@ -565,13 +565,13 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>18.1042</v>
+        <v>16.6016</v>
       </c>
       <c r="E2" t="n">
-        <v>21.2024</v>
+        <v>20.8984</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.0984</v>
+        <v>-4.2968</v>
       </c>
       <c r="G2" t="n">
         <v>8.3927</v>
@@ -610,13 +610,13 @@
         <v>14.8461</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7604</v>
+        <v>-2.263</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.4009</v>
+        <v>-2.7049</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6404</v>
+        <v>0.4419</v>
       </c>
       <c r="V2" t="n">
         <v>6.3698</v>
@@ -643,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1279</v>
+        <v>-0.07339999999999999</v>
       </c>
       <c r="E3" t="n">
         <v>-0.7547</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6268</v>
+        <v>0.6813</v>
       </c>
       <c r="G3" t="n">
         <v>-0.02940000000000001</v>
@@ -688,13 +688,13 @@
         <v>0.1953</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2938</v>
+        <v>-0.2394</v>
       </c>
       <c r="T3" t="n">
         <v>-0.121</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1728</v>
+        <v>-0.1183</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.0157</v>
+        <v>-1.0623</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.1808</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.8815</v>
       </c>
       <c r="G4" t="n">
         <v>-1.8609</v>
@@ -766,13 +766,13 @@
         <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2592</v>
+        <v>0.2126</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4925</v>
+        <v>0.3914</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2333</v>
+        <v>-0.1789</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. ARNELLA I MAS</t>
+          <t>R. GUARDIOLA I DISPÉS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.0882</v>
+        <v>-1.3588</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8107</v>
+        <v>1.1493</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2775</v>
+        <v>-2.5081</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2947</v>
+        <v>3.2396</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7416</v>
+        <v>2.5641</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5531</v>
+        <v>0.6755</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4708</v>
+        <v>7.224</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0819</v>
+        <v>4.794</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5527</v>
+        <v>2.4299</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8239</v>
+        <v>-3.9844</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8235</v>
+        <v>-2.23</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0004</v>
+        <v>-1.7545</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3907</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>-4.8836</v>
       </c>
       <c r="R5" t="n">
-        <v>0.586</v>
+        <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4028</v>
+        <v>-1.8887</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3631</v>
+        <v>-1.8004</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0397</v>
+        <v>-0.0882</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3655999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.9748999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA I DISPÉS</t>
+          <t>R. ARNELLA I MAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.7513</v>
+        <v>-1.8237</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5426000000000002</v>
+        <v>-1.7096</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.2938</v>
+        <v>-0.1141</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2396</v>
+        <v>-1.2947</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5641</v>
+        <v>-0.7416</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6755</v>
+        <v>-0.5531</v>
       </c>
       <c r="J6" t="n">
-        <v>7.224</v>
+        <v>-0.4708</v>
       </c>
       <c r="K6" t="n">
-        <v>4.794</v>
+        <v>0.0819</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4299</v>
+        <v>-0.5527</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.9844</v>
+        <v>-0.8239</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.23</v>
+        <v>-0.8235</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7545</v>
+        <v>-0.0004</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.3441</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8836</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5395</v>
+        <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.2811</v>
+        <v>-0.1383</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.4072</v>
+        <v>-0.262</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8741</v>
+        <v>0.1238</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3655999999999999</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9748999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4476</v>
+        <v>-3.2104</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5569</v>
+        <v>-1.4558</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8907</v>
+        <v>-1.7546</v>
       </c>
       <c r="G7" t="n">
         <v>-2.6498</v>
@@ -1000,13 +1000,13 @@
         <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9931000000000001</v>
+        <v>-0.7559</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5447</v>
+        <v>-0.4435</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4485</v>
+        <v>-0.3123</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.4703</v>
+        <v>-7.2066</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.5012</v>
+        <v>-6.209</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.969</v>
+        <v>-0.9975999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-4.799099999999999</v>
@@ -1078,13 +1078,13 @@
         <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3180999999999999</v>
+        <v>-1.0545</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6358000000000001</v>
+        <v>-0.0721</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9538</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0.2097</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. RIVAS POMEROL</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>-14.487</v>
+        <v>-9.3405</v>
       </c>
       <c r="E9" t="n">
-        <v>-13.3701</v>
+        <v>1.0687</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1166</v>
+        <v>-10.4091</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.7624</v>
+        <v>-12.1089</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.3545</v>
+        <v>-20.6723</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5921999999999999</v>
+        <v>8.563499999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>6.883599999999999</v>
+        <v>11.0596</v>
       </c>
       <c r="K9" t="n">
-        <v>5.0713</v>
+        <v>-0.4840000000000002</v>
       </c>
       <c r="L9" t="n">
-        <v>1.812</v>
+        <v>11.5438</v>
       </c>
       <c r="M9" t="n">
-        <v>-9.645899999999999</v>
+        <v>-23.1688</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.4262</v>
+        <v>-20.1884</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2199</v>
+        <v>-2.9802</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.7116</v>
+        <v>0.3908000000000006</v>
       </c>
       <c r="Q9" t="n">
-        <v>-18.7527</v>
+        <v>-25.0038</v>
       </c>
       <c r="R9" t="n">
-        <v>15.0415</v>
+        <v>25.3945</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.7703</v>
+        <v>-9.1218</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.7773</v>
+        <v>-8.698700000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9930999999999999</v>
+        <v>-0.4231999999999998</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.242599999999999</v>
+        <v>11.4996</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2764</v>
+        <v>23.7114</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.519</v>
+        <v>-12.2116</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>-15.122</v>
+        <v>-16.3599</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1951999999999998</v>
+        <v>-2.711400000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-14.9268</v>
+        <v>-13.6485</v>
       </c>
       <c r="G10" t="n">
-        <v>5.790900000000001</v>
+        <v>-11.6055</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9921000000000006</v>
+        <v>-11.9628</v>
       </c>
       <c r="I10" t="n">
-        <v>4.7991</v>
+        <v>0.3573999999999997</v>
       </c>
       <c r="J10" t="n">
-        <v>39.524</v>
+        <v>17.1467</v>
       </c>
       <c r="K10" t="n">
-        <v>24.5913</v>
+        <v>3.692</v>
       </c>
       <c r="L10" t="n">
-        <v>14.9327</v>
+        <v>13.4544</v>
       </c>
       <c r="M10" t="n">
-        <v>-33.7331</v>
+        <v>-28.7522</v>
       </c>
       <c r="N10" t="n">
-        <v>-23.5989</v>
+        <v>-15.6549</v>
       </c>
       <c r="O10" t="n">
-        <v>-10.134</v>
+        <v>-13.0973</v>
       </c>
       <c r="P10" t="n">
-        <v>-20.7063</v>
+        <v>-3.7116</v>
       </c>
       <c r="Q10" t="n">
-        <v>-59.3839</v>
+        <v>-32.8176</v>
       </c>
       <c r="R10" t="n">
-        <v>38.6779</v>
+        <v>29.1059</v>
       </c>
       <c r="S10" t="n">
-        <v>-8.424799999999999</v>
+        <v>-7.248</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.4895</v>
+        <v>-6.0447</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.9355</v>
+        <v>-1.2033</v>
       </c>
       <c r="V10" t="n">
-        <v>8.218500000000001</v>
+        <v>6.205500000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>26.1547</v>
+        <v>19.0043</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.9357</v>
+        <v>-12.799</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>A. RIVAS POMEROL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.403</v>
+        <v>-16.5692</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.054100000000001</v>
+        <v>-14.9282</v>
       </c>
       <c r="F11" t="n">
-        <v>-14.3487</v>
+        <v>-1.6409</v>
       </c>
       <c r="G11" t="n">
-        <v>-12.1089</v>
+        <v>-2.7624</v>
       </c>
       <c r="H11" t="n">
-        <v>-20.6723</v>
+        <v>-3.3545</v>
       </c>
       <c r="I11" t="n">
-        <v>8.563499999999999</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>11.0596</v>
+        <v>6.883599999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4840000000000002</v>
+        <v>5.0713</v>
       </c>
       <c r="L11" t="n">
-        <v>11.5438</v>
+        <v>1.812</v>
       </c>
       <c r="M11" t="n">
-        <v>-23.1688</v>
+        <v>-9.645899999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-20.1884</v>
+        <v>-8.4262</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.9802</v>
+        <v>-1.2199</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3908000000000006</v>
+        <v>-3.7116</v>
       </c>
       <c r="Q11" t="n">
-        <v>-25.0038</v>
+        <v>-18.7527</v>
       </c>
       <c r="R11" t="n">
-        <v>25.3945</v>
+        <v>15.0415</v>
       </c>
       <c r="S11" t="n">
-        <v>-15.184</v>
+        <v>-5.8526</v>
       </c>
       <c r="T11" t="n">
-        <v>-10.8215</v>
+        <v>-4.3353</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.3626</v>
+        <v>-1.5172</v>
       </c>
       <c r="V11" t="n">
-        <v>11.4996</v>
+        <v>-4.242599999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>23.7114</v>
+        <v>1.2764</v>
       </c>
       <c r="X11" t="n">
-        <v>-12.2116</v>
+        <v>-5.519</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>-20.2619</v>
+        <v>-17.1284</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.138400000000001</v>
+        <v>-2.946800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.1236</v>
+        <v>-14.1815</v>
       </c>
       <c r="G12" t="n">
-        <v>-17.0678</v>
+        <v>5.790900000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-17.3496</v>
+        <v>0.9921000000000006</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2819</v>
+        <v>4.7991</v>
       </c>
       <c r="J12" t="n">
-        <v>14.8389</v>
+        <v>39.524</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8894</v>
+        <v>24.5913</v>
       </c>
       <c r="L12" t="n">
-        <v>10.9497</v>
+        <v>14.9327</v>
       </c>
       <c r="M12" t="n">
-        <v>-31.9069</v>
+        <v>-33.7331</v>
       </c>
       <c r="N12" t="n">
-        <v>-21.239</v>
+        <v>-23.5989</v>
       </c>
       <c r="O12" t="n">
-        <v>-10.6676</v>
+        <v>-10.134</v>
       </c>
       <c r="P12" t="n">
-        <v>8.399699999999999</v>
+        <v>-20.7063</v>
       </c>
       <c r="Q12" t="n">
-        <v>-24.8084</v>
+        <v>-59.3839</v>
       </c>
       <c r="R12" t="n">
-        <v>33.2082</v>
+        <v>38.6779</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.076099999999999</v>
+        <v>-10.4318</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.4802</v>
+        <v>-9.241300000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4042000000000001</v>
+        <v>-1.1904</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.5176</v>
+        <v>8.218500000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>7.311599999999999</v>
+        <v>26.1547</v>
       </c>
       <c r="X12" t="n">
-        <v>-13.8292</v>
+        <v>-17.9357</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.7824</v>
+        <v>-21.4179</v>
       </c>
       <c r="E13" t="n">
-        <v>-21.4039</v>
+        <v>-2.6971</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3785000000000003</v>
+        <v>-18.7209</v>
       </c>
       <c r="G13" t="n">
-        <v>-17.1592</v>
+        <v>-6.126299999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.2798</v>
+        <v>-12.2223</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.8796</v>
+        <v>6.0959</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2266</v>
+        <v>25.4687</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2589</v>
+        <v>10.3157</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03249999999999997</v>
+        <v>15.1527</v>
       </c>
       <c r="M13" t="n">
-        <v>-15.9329</v>
+        <v>-31.5951</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.020700000000001</v>
+        <v>-22.5381</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.912099999999999</v>
+        <v>-9.056900000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1721</v>
+        <v>20.7063</v>
       </c>
       <c r="Q13" t="n">
-        <v>-22.8548</v>
+        <v>-24.027</v>
       </c>
       <c r="R13" t="n">
-        <v>21.6832</v>
+        <v>44.7333</v>
       </c>
       <c r="S13" t="n">
-        <v>7.920299999999999</v>
+        <v>-11.985</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5637000000000001</v>
+        <v>-11.0088</v>
       </c>
       <c r="U13" t="n">
-        <v>7.3566</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-11.3713</v>
+        <v>-24.0129</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1141</v>
+        <v>6.8698</v>
       </c>
       <c r="X13" t="n">
-        <v>-13.4853</v>
+        <v>-30.8829</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-24.4352</v>
+        <v>-24.1694</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.95</v>
+        <v>-10.8092</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.4853</v>
+        <v>-13.3603</v>
       </c>
       <c r="G14" t="n">
-        <v>-15.8363</v>
+        <v>-17.0678</v>
       </c>
       <c r="H14" t="n">
-        <v>-12.5366</v>
+        <v>-17.3496</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.2995</v>
+        <v>0.2819</v>
       </c>
       <c r="J14" t="n">
-        <v>7.7692</v>
+        <v>14.8389</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8878</v>
+        <v>3.8894</v>
       </c>
       <c r="L14" t="n">
-        <v>5.8814</v>
+        <v>10.9497</v>
       </c>
       <c r="M14" t="n">
-        <v>-23.6053</v>
+        <v>-31.9069</v>
       </c>
       <c r="N14" t="n">
-        <v>-14.4243</v>
+        <v>-21.239</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.180899999999999</v>
+        <v>-10.6676</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.7114</v>
+        <v>8.399699999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-24.6133</v>
+        <v>-24.8084</v>
       </c>
       <c r="R14" t="n">
-        <v>20.9017</v>
+        <v>33.2082</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9246</v>
+        <v>-8.983499999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6471999999999997</v>
+        <v>-8.1515</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5718</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.811999999999999</v>
+        <v>-6.5176</v>
       </c>
       <c r="W14" t="n">
-        <v>5.5416</v>
+        <v>7.311599999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.3537</v>
+        <v>-13.8292</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>R. GUARDIOLA DISPES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>-24.7738</v>
+        <v>-26.0675</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.17</v>
+        <v>-13.3755</v>
       </c>
       <c r="F15" t="n">
-        <v>-16.6037</v>
+        <v>-12.6919</v>
       </c>
       <c r="G15" t="n">
-        <v>-11.6055</v>
+        <v>-10.5267</v>
       </c>
       <c r="H15" t="n">
-        <v>-11.9628</v>
+        <v>-13.4985</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3573999999999997</v>
+        <v>2.971699999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>17.1467</v>
+        <v>8.124000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>3.692</v>
+        <v>-0.3865000000000005</v>
       </c>
       <c r="L15" t="n">
-        <v>13.4544</v>
+        <v>8.5106</v>
       </c>
       <c r="M15" t="n">
-        <v>-28.7522</v>
+        <v>-18.6506</v>
       </c>
       <c r="N15" t="n">
-        <v>-15.6549</v>
+        <v>-13.1119</v>
       </c>
       <c r="O15" t="n">
-        <v>-13.0973</v>
+        <v>-5.5388</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.7116</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q15" t="n">
-        <v>-32.8176</v>
+        <v>-23.2458</v>
       </c>
       <c r="R15" t="n">
-        <v>29.1059</v>
+        <v>21.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>-15.6618</v>
+        <v>-6.2005</v>
       </c>
       <c r="T15" t="n">
-        <v>-11.5034</v>
+        <v>-3.0185</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.1584</v>
+        <v>-3.182</v>
       </c>
       <c r="V15" t="n">
-        <v>6.205500000000001</v>
+        <v>-7.7774</v>
       </c>
       <c r="W15" t="n">
-        <v>19.0043</v>
+        <v>4.7647</v>
       </c>
       <c r="X15" t="n">
-        <v>-12.799</v>
+        <v>-12.5421</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>-27.159</v>
+        <v>-27.2074</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.982300000000001</v>
+        <v>-6.6248</v>
       </c>
       <c r="F16" t="n">
-        <v>-20.1766</v>
+        <v>-20.5829</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.126299999999998</v>
+        <v>-11.4427</v>
       </c>
       <c r="H16" t="n">
-        <v>-12.2223</v>
+        <v>-8.428699999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>6.0959</v>
+        <v>-3.014</v>
       </c>
       <c r="J16" t="n">
-        <v>25.4687</v>
+        <v>21.4613</v>
       </c>
       <c r="K16" t="n">
-        <v>10.3157</v>
+        <v>11.9172</v>
       </c>
       <c r="L16" t="n">
-        <v>15.1527</v>
+        <v>9.543999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-31.5951</v>
+        <v>-32.9038</v>
       </c>
       <c r="N16" t="n">
-        <v>-22.5381</v>
+        <v>-20.3459</v>
       </c>
       <c r="O16" t="n">
-        <v>-9.056900000000001</v>
+        <v>-12.5577</v>
       </c>
       <c r="P16" t="n">
-        <v>20.7063</v>
+        <v>12.3068</v>
       </c>
       <c r="Q16" t="n">
-        <v>-24.027</v>
+        <v>-22.2689</v>
       </c>
       <c r="R16" t="n">
-        <v>44.7333</v>
+        <v>34.5756</v>
       </c>
       <c r="S16" t="n">
-        <v>-17.7259</v>
+        <v>-10.8296</v>
       </c>
       <c r="T16" t="n">
-        <v>-15.2938</v>
+        <v>-7.0936</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.432</v>
+        <v>-3.7361</v>
       </c>
       <c r="V16" t="n">
-        <v>-24.0129</v>
+        <v>-17.2417</v>
       </c>
       <c r="W16" t="n">
-        <v>6.8698</v>
+        <v>1.2763</v>
       </c>
       <c r="X16" t="n">
-        <v>-30.8829</v>
+        <v>-18.5182</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>-28.8731</v>
+        <v>-27.2449</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.3406</v>
+        <v>-23.6705</v>
       </c>
       <c r="F17" t="n">
-        <v>-22.5326</v>
+        <v>-3.5745</v>
       </c>
       <c r="G17" t="n">
-        <v>-11.4427</v>
+        <v>-17.1592</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.428699999999999</v>
+        <v>-8.2798</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.014</v>
+        <v>-8.8796</v>
       </c>
       <c r="J17" t="n">
-        <v>21.4613</v>
+        <v>-1.2266</v>
       </c>
       <c r="K17" t="n">
-        <v>11.9172</v>
+        <v>-1.2589</v>
       </c>
       <c r="L17" t="n">
-        <v>9.543999999999999</v>
+        <v>0.03249999999999997</v>
       </c>
       <c r="M17" t="n">
-        <v>-32.9038</v>
+        <v>-15.9329</v>
       </c>
       <c r="N17" t="n">
-        <v>-20.3459</v>
+        <v>-7.020700000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-12.5577</v>
+        <v>-8.912099999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>12.3068</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-22.2689</v>
+        <v>-22.8548</v>
       </c>
       <c r="R17" t="n">
-        <v>34.5756</v>
+        <v>21.6832</v>
       </c>
       <c r="S17" t="n">
-        <v>-12.4958</v>
+        <v>2.4577</v>
       </c>
       <c r="T17" t="n">
-        <v>-6.8094</v>
+        <v>-1.703</v>
       </c>
       <c r="U17" t="n">
-        <v>-5.686</v>
+        <v>4.160600000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-17.2417</v>
+        <v>-11.3713</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2763</v>
+        <v>2.1141</v>
       </c>
       <c r="X17" t="n">
-        <v>-18.5182</v>
+        <v>-13.4853</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA DISPES</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>-29.7171</v>
+        <v>-28.0092</v>
       </c>
       <c r="E18" t="n">
-        <v>-15.7205</v>
+        <v>-14.1554</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.9964</v>
+        <v>-13.8538</v>
       </c>
       <c r="G18" t="n">
-        <v>-10.5267</v>
+        <v>-15.8363</v>
       </c>
       <c r="H18" t="n">
-        <v>-13.4985</v>
+        <v>-12.5366</v>
       </c>
       <c r="I18" t="n">
-        <v>2.971699999999999</v>
+        <v>-3.2995</v>
       </c>
       <c r="J18" t="n">
-        <v>8.124000000000001</v>
+        <v>7.7692</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3865000000000005</v>
+        <v>1.8878</v>
       </c>
       <c r="L18" t="n">
-        <v>8.5106</v>
+        <v>5.8814</v>
       </c>
       <c r="M18" t="n">
-        <v>-18.6506</v>
+        <v>-23.6053</v>
       </c>
       <c r="N18" t="n">
-        <v>-13.1119</v>
+        <v>-14.4243</v>
       </c>
       <c r="O18" t="n">
-        <v>-5.5388</v>
+        <v>-9.180899999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5627</v>
+        <v>-3.7114</v>
       </c>
       <c r="Q18" t="n">
-        <v>-23.2458</v>
+        <v>-24.6133</v>
       </c>
       <c r="R18" t="n">
-        <v>21.6829</v>
+        <v>20.9017</v>
       </c>
       <c r="S18" t="n">
-        <v>-9.850300000000001</v>
+        <v>-0.6494000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-5.3636</v>
+        <v>-2.8526</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.4866</v>
+        <v>2.2034</v>
       </c>
       <c r="V18" t="n">
-        <v>-7.7774</v>
+        <v>-7.811999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>4.7647</v>
+        <v>5.5416</v>
       </c>
       <c r="X18" t="n">
-        <v>-12.5421</v>
+        <v>-13.3537</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>-62.6692</v>
+        <v>-56.2093</v>
       </c>
       <c r="E19" t="n">
-        <v>-31.7799</v>
+        <v>-29.7987</v>
       </c>
       <c r="F19" t="n">
-        <v>-30.8897</v>
+        <v>-26.4104</v>
       </c>
       <c r="G19" t="n">
         <v>-38.9941</v>
@@ -1936,13 +1936,13 @@
         <v>29.6924</v>
       </c>
       <c r="S19" t="n">
-        <v>-17.5061</v>
+        <v>-11.0464</v>
       </c>
       <c r="T19" t="n">
-        <v>-9.660299999999999</v>
+        <v>-7.6792</v>
       </c>
       <c r="U19" t="n">
-        <v>-7.8456</v>
+        <v>-3.3669</v>
       </c>
       <c r="V19" t="n">
         <v>-4.020299999999999</v>
@@ -1969,13 +1969,13 @@
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>-69.7914</v>
+        <v>-65.2516</v>
       </c>
       <c r="E20" t="n">
-        <v>-44.6745</v>
+        <v>-42.4715</v>
       </c>
       <c r="F20" t="n">
-        <v>-25.1171</v>
+        <v>-22.7803</v>
       </c>
       <c r="G20" t="n">
         <v>-45.7031</v>
@@ -2014,13 +2014,13 @@
         <v>26.3712</v>
       </c>
       <c r="S20" t="n">
-        <v>-17.2927</v>
+        <v>-12.7529</v>
       </c>
       <c r="T20" t="n">
-        <v>-9.9824</v>
+        <v>-7.7792</v>
       </c>
       <c r="U20" t="n">
-        <v>-7.3103</v>
+        <v>-4.9735</v>
       </c>
       <c r="V20" t="n">
         <v>1.9949</v>
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-352.2719</v>
+        <v>-333.1088</v>
       </c>
       <c r="E21" t="n">
-        <v>-157.7377</v>
+        <v>-151.3826</v>
       </c>
       <c r="F21" t="n">
-        <v>-194.5342</v>
+        <v>-181.7264</v>
       </c>
       <c r="G21" t="n">
         <v>-182.5437</v>
@@ -2062,7 +2062,7 @@
         <v>-153.5501</v>
       </c>
       <c r="I21" t="n">
-        <v>-28.9927</v>
+        <v>-28.99270000000001</v>
       </c>
       <c r="J21" t="n">
         <v>154.0324</v>
@@ -2083,7 +2083,7 @@
         <v>-120.8723</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.9297</v>
+        <v>-2.929700000000004</v>
       </c>
       <c r="Q21" t="n">
         <v>-364.3126</v>
@@ -2092,13 +2092,13 @@
         <v>361.3839</v>
       </c>
       <c r="S21" t="n">
-        <v>-117.933</v>
+        <v>-98.771</v>
       </c>
       <c r="T21" t="n">
-        <v>-88.97350000000002</v>
+        <v>-82.6189</v>
       </c>
       <c r="U21" t="n">
-        <v>-28.9593</v>
+        <v>-16.1515</v>
       </c>
       <c r="V21" t="n">
         <v>-48.86339999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB QUART GRUES CRUZ.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB QUART GRUES CRUZ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. ARNELLA MAS</t>
+          <t>R. GUARDIOLA I DISPÉS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.07339999999999999</v>
+        <v>3.9558</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7547</v>
+        <v>3.9558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6813</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.02940000000000001</v>
+        <v>3.9558</v>
       </c>
       <c r="H3" t="n">
-        <v>0.065</v>
+        <v>0.921</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09439999999999998</v>
+        <v>3.035</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.6336000000000001</v>
+        <v>3.9558</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.921</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6336000000000001</v>
+        <v>3.035</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6042</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5393</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2394</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.121</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1183</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. PARADINAS DELGADO</t>
+          <t>À. ANTEQUERA SOLER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.0623</v>
+        <v>0.307</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1808</v>
+        <v>0.307</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8815</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.8609</v>
+        <v>0.307</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1481</v>
+        <v>0.307</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7128</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5722</v>
+        <v>0.307</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0614</v>
+        <v>0.307</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2887</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2095</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0792</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2126</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3914</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1789</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA I DISPÉS</t>
+          <t>R. ARNELLA MAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3588</v>
+        <v>-0.07339999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1493</v>
+        <v>-0.7547</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5081</v>
+        <v>0.6813</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2396</v>
+        <v>-0.02940000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5641</v>
+        <v>0.065</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6755</v>
+        <v>-0.09439999999999998</v>
       </c>
       <c r="J5" t="n">
-        <v>7.224</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>4.794</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4299</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.9844</v>
+        <v>0.6042</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.23</v>
+        <v>0.065</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7545</v>
+        <v>0.5393</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.3441</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5395</v>
+        <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8887</v>
+        <v>-0.2394</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.8004</v>
+        <v>-0.121</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0882</v>
+        <v>-0.1183</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3655999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9748999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. ARNELLA I MAS</t>
+          <t>E. PARADINAS DELGADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8237</v>
+        <v>-1.0623</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7096</v>
+        <v>-0.1808</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1141</v>
+        <v>-0.8815</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2947</v>
+        <v>-1.8609</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7416</v>
+        <v>-0.1481</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5531</v>
+        <v>-1.7128</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4708</v>
+        <v>-0.5722</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0819</v>
+        <v>0.0614</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5527</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8239</v>
+        <v>-1.2887</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8235</v>
+        <v>-0.2095</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0004</v>
+        <v>-1.0792</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1383</v>
+        <v>0.2126</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.262</v>
+        <v>0.3914</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1238</v>
+        <v>-0.1789</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>À. ANTEQUERA SOLER</t>
+          <t>R. ARNELLA I MAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,61 +952,61 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.2104</v>
+        <v>-1.8237</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4558</v>
+        <v>-1.7096</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7546</v>
+        <v>-0.1141</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6498</v>
+        <v>-1.2947</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3423</v>
+        <v>-0.7416</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3075</v>
+        <v>-0.5531</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0122</v>
+        <v>-0.4708</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2443</v>
+        <v>0.0819</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7679000000000002</v>
+        <v>-0.5527</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6377</v>
+        <v>-0.8239</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.098</v>
+        <v>-0.8235</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5397000000000001</v>
+        <v>-0.0004</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7559</v>
+        <v>-0.1383</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4435</v>
+        <v>-0.262</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3123</v>
+        <v>0.1238</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BALLO RODRIGUEZ</t>
+          <t>A. ANTEQUERA SOLER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.2066</v>
+        <v>-3.5174</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.209</v>
+        <v>-1.7628</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9975999999999999</v>
+        <v>-1.7546</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.799099999999999</v>
+        <v>-2.9568</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.6636</v>
+        <v>-1.6493</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1354</v>
+        <v>-1.3075</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.2068</v>
+        <v>-1.3192</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.5327</v>
+        <v>-0.5513</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6741</v>
+        <v>-0.7679000000000002</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5923</v>
+        <v>-1.6377</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.131</v>
+        <v>-1.098</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5387</v>
+        <v>-0.5397000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0545</v>
+        <v>-0.7559</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0721</v>
+        <v>-0.4435</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-0.3123</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2097</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>R. GUARDIOLA I DISPES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.3405</v>
+        <v>-5.3147</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0687</v>
+        <v>-2.8066</v>
       </c>
       <c r="F9" t="n">
-        <v>-10.4091</v>
+        <v>-2.5081</v>
       </c>
       <c r="G9" t="n">
-        <v>-12.1089</v>
+        <v>-0.7162999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-20.6723</v>
+        <v>1.6432</v>
       </c>
       <c r="I9" t="n">
-        <v>8.563499999999999</v>
+        <v>-2.3595</v>
       </c>
       <c r="J9" t="n">
-        <v>11.0596</v>
+        <v>3.2681</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4840000000000002</v>
+        <v>3.8731</v>
       </c>
       <c r="L9" t="n">
-        <v>11.5438</v>
+        <v>-0.605</v>
       </c>
       <c r="M9" t="n">
-        <v>-23.1688</v>
+        <v>-3.9844</v>
       </c>
       <c r="N9" t="n">
-        <v>-20.1884</v>
+        <v>-2.23</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.9802</v>
+        <v>-1.7545</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3908000000000006</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q9" t="n">
-        <v>-25.0038</v>
+        <v>-4.8836</v>
       </c>
       <c r="R9" t="n">
-        <v>25.3945</v>
+        <v>2.5395</v>
       </c>
       <c r="S9" t="n">
-        <v>-9.1218</v>
+        <v>-1.8887</v>
       </c>
       <c r="T9" t="n">
-        <v>-8.698700000000001</v>
+        <v>-1.8004</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4231999999999998</v>
+        <v>-0.0882</v>
       </c>
       <c r="V9" t="n">
-        <v>11.4996</v>
+        <v>-0.3655999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>23.7114</v>
+        <v>0.6093</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.2116</v>
+        <v>-0.9748999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>D. BALLO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-16.3599</v>
+        <v>-7.2066</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.711400000000001</v>
+        <v>-6.209</v>
       </c>
       <c r="F10" t="n">
-        <v>-13.6485</v>
+        <v>-0.9975999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-11.6055</v>
+        <v>-4.799099999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-11.9628</v>
+        <v>-4.6636</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3573999999999997</v>
+        <v>-0.1354</v>
       </c>
       <c r="J10" t="n">
-        <v>17.1467</v>
+        <v>-3.2068</v>
       </c>
       <c r="K10" t="n">
-        <v>3.692</v>
+        <v>-2.5327</v>
       </c>
       <c r="L10" t="n">
-        <v>13.4544</v>
+        <v>-0.6741</v>
       </c>
       <c r="M10" t="n">
-        <v>-28.7522</v>
+        <v>-1.5923</v>
       </c>
       <c r="N10" t="n">
-        <v>-15.6549</v>
+        <v>-2.131</v>
       </c>
       <c r="O10" t="n">
-        <v>-13.0973</v>
+        <v>0.5387</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.7116</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q10" t="n">
-        <v>-32.8176</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>29.1059</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-7.248</v>
+        <v>-1.0545</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.0447</v>
+        <v>-0.0721</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2033</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>6.205500000000001</v>
+        <v>0.2097</v>
       </c>
       <c r="W10" t="n">
-        <v>19.0043</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-12.799</v>
+        <v>0.2097</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RIVAS POMEROL</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>-16.5692</v>
+        <v>-9.3405</v>
       </c>
       <c r="E11" t="n">
-        <v>-14.9282</v>
+        <v>1.0687</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6409</v>
+        <v>-10.4091</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7624</v>
+        <v>-12.1089</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.3545</v>
+        <v>-20.6723</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5921999999999999</v>
+        <v>8.563499999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>6.883599999999999</v>
+        <v>11.0596</v>
       </c>
       <c r="K11" t="n">
-        <v>5.0713</v>
+        <v>-0.4840000000000002</v>
       </c>
       <c r="L11" t="n">
-        <v>1.812</v>
+        <v>11.5438</v>
       </c>
       <c r="M11" t="n">
-        <v>-9.645899999999999</v>
+        <v>-23.1688</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.4262</v>
+        <v>-20.1884</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2199</v>
+        <v>-2.9802</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.7116</v>
+        <v>0.3908000000000006</v>
       </c>
       <c r="Q11" t="n">
-        <v>-18.7527</v>
+        <v>-25.0038</v>
       </c>
       <c r="R11" t="n">
-        <v>15.0415</v>
+        <v>25.3945</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.8526</v>
+        <v>-9.1218</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.3353</v>
+        <v>-8.698700000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5172</v>
+        <v>-0.4231999999999998</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.242599999999999</v>
+        <v>11.4996</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2764</v>
+        <v>23.7114</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.519</v>
+        <v>-12.2116</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>-17.1284</v>
+        <v>-16.3599</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.946800000000001</v>
+        <v>-2.711400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.1815</v>
+        <v>-13.6485</v>
       </c>
       <c r="G12" t="n">
-        <v>5.790900000000001</v>
+        <v>-11.6055</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9921000000000006</v>
+        <v>-11.9628</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7991</v>
+        <v>0.3573999999999997</v>
       </c>
       <c r="J12" t="n">
-        <v>39.524</v>
+        <v>17.1467</v>
       </c>
       <c r="K12" t="n">
-        <v>24.5913</v>
+        <v>3.692</v>
       </c>
       <c r="L12" t="n">
-        <v>14.9327</v>
+        <v>13.4544</v>
       </c>
       <c r="M12" t="n">
-        <v>-33.7331</v>
+        <v>-28.7522</v>
       </c>
       <c r="N12" t="n">
-        <v>-23.5989</v>
+        <v>-15.6549</v>
       </c>
       <c r="O12" t="n">
-        <v>-10.134</v>
+        <v>-13.0973</v>
       </c>
       <c r="P12" t="n">
-        <v>-20.7063</v>
+        <v>-3.7116</v>
       </c>
       <c r="Q12" t="n">
-        <v>-59.3839</v>
+        <v>-32.8176</v>
       </c>
       <c r="R12" t="n">
-        <v>38.6779</v>
+        <v>29.1059</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.4318</v>
+        <v>-7.248</v>
       </c>
       <c r="T12" t="n">
-        <v>-9.241300000000001</v>
+        <v>-6.0447</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1904</v>
+        <v>-1.2033</v>
       </c>
       <c r="V12" t="n">
-        <v>8.218500000000001</v>
+        <v>6.205500000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>26.1547</v>
+        <v>19.0043</v>
       </c>
       <c r="X12" t="n">
-        <v>-17.9357</v>
+        <v>-12.799</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>A. RIVAS POMEROL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.4179</v>
+        <v>-16.5692</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6971</v>
+        <v>-14.9282</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.7209</v>
+        <v>-1.6409</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.126299999999998</v>
+        <v>-2.7624</v>
       </c>
       <c r="H13" t="n">
-        <v>-12.2223</v>
+        <v>-3.3545</v>
       </c>
       <c r="I13" t="n">
-        <v>6.0959</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>25.4687</v>
+        <v>6.883599999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>10.3157</v>
+        <v>5.0713</v>
       </c>
       <c r="L13" t="n">
-        <v>15.1527</v>
+        <v>1.812</v>
       </c>
       <c r="M13" t="n">
-        <v>-31.5951</v>
+        <v>-9.645899999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-22.5381</v>
+        <v>-8.4262</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.056900000000001</v>
+        <v>-1.2199</v>
       </c>
       <c r="P13" t="n">
-        <v>20.7063</v>
+        <v>-3.7116</v>
       </c>
       <c r="Q13" t="n">
-        <v>-24.027</v>
+        <v>-18.7527</v>
       </c>
       <c r="R13" t="n">
-        <v>44.7333</v>
+        <v>15.0415</v>
       </c>
       <c r="S13" t="n">
-        <v>-11.985</v>
+        <v>-5.8526</v>
       </c>
       <c r="T13" t="n">
-        <v>-11.0088</v>
+        <v>-4.3353</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-1.5172</v>
       </c>
       <c r="V13" t="n">
-        <v>-24.0129</v>
+        <v>-4.242599999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>6.8698</v>
+        <v>1.2764</v>
       </c>
       <c r="X13" t="n">
-        <v>-30.8829</v>
+        <v>-5.519</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-24.1694</v>
+        <v>-17.1284</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.8092</v>
+        <v>-2.946800000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.3603</v>
+        <v>-14.1815</v>
       </c>
       <c r="G14" t="n">
-        <v>-17.0678</v>
+        <v>5.790900000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-17.3496</v>
+        <v>0.9921000000000006</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2819</v>
+        <v>4.7991</v>
       </c>
       <c r="J14" t="n">
-        <v>14.8389</v>
+        <v>39.524</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8894</v>
+        <v>24.5913</v>
       </c>
       <c r="L14" t="n">
-        <v>10.9497</v>
+        <v>14.9327</v>
       </c>
       <c r="M14" t="n">
-        <v>-31.9069</v>
+        <v>-33.7331</v>
       </c>
       <c r="N14" t="n">
-        <v>-21.239</v>
+        <v>-23.5989</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.6676</v>
+        <v>-10.134</v>
       </c>
       <c r="P14" t="n">
-        <v>8.399699999999999</v>
+        <v>-20.7063</v>
       </c>
       <c r="Q14" t="n">
-        <v>-24.8084</v>
+        <v>-59.3839</v>
       </c>
       <c r="R14" t="n">
-        <v>33.2082</v>
+        <v>38.6779</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.983499999999999</v>
+        <v>-10.4318</v>
       </c>
       <c r="T14" t="n">
-        <v>-8.1515</v>
+        <v>-9.241300000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-1.1904</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.5176</v>
+        <v>8.218500000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>7.311599999999999</v>
+        <v>26.1547</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.8292</v>
+        <v>-17.9357</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA DISPES</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-26.0675</v>
+        <v>-21.4179</v>
       </c>
       <c r="E15" t="n">
-        <v>-13.3755</v>
+        <v>-2.6971</v>
       </c>
       <c r="F15" t="n">
-        <v>-12.6919</v>
+        <v>-18.7209</v>
       </c>
       <c r="G15" t="n">
-        <v>-10.5267</v>
+        <v>-6.126299999999998</v>
       </c>
       <c r="H15" t="n">
-        <v>-13.4985</v>
+        <v>-12.2223</v>
       </c>
       <c r="I15" t="n">
-        <v>2.971699999999999</v>
+        <v>6.0959</v>
       </c>
       <c r="J15" t="n">
-        <v>8.124000000000001</v>
+        <v>25.4687</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3865000000000005</v>
+        <v>10.3157</v>
       </c>
       <c r="L15" t="n">
-        <v>8.5106</v>
+        <v>15.1527</v>
       </c>
       <c r="M15" t="n">
-        <v>-18.6506</v>
+        <v>-31.5951</v>
       </c>
       <c r="N15" t="n">
-        <v>-13.1119</v>
+        <v>-22.5381</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.5388</v>
+        <v>-9.056900000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5627</v>
+        <v>20.7063</v>
       </c>
       <c r="Q15" t="n">
-        <v>-23.2458</v>
+        <v>-24.027</v>
       </c>
       <c r="R15" t="n">
-        <v>21.6829</v>
+        <v>44.7333</v>
       </c>
       <c r="S15" t="n">
-        <v>-6.2005</v>
+        <v>-11.985</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.0185</v>
+        <v>-11.0088</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.182</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-7.7774</v>
+        <v>-24.0129</v>
       </c>
       <c r="W15" t="n">
-        <v>4.7647</v>
+        <v>6.8698</v>
       </c>
       <c r="X15" t="n">
-        <v>-12.5421</v>
+        <v>-30.8829</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>-27.2074</v>
+        <v>-24.1694</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.6248</v>
+        <v>-10.8092</v>
       </c>
       <c r="F16" t="n">
-        <v>-20.5829</v>
+        <v>-13.3603</v>
       </c>
       <c r="G16" t="n">
-        <v>-11.4427</v>
+        <v>-17.0678</v>
       </c>
       <c r="H16" t="n">
-        <v>-8.428699999999999</v>
+        <v>-17.3496</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.014</v>
+        <v>0.2819</v>
       </c>
       <c r="J16" t="n">
-        <v>21.4613</v>
+        <v>14.8389</v>
       </c>
       <c r="K16" t="n">
-        <v>11.9172</v>
+        <v>3.8894</v>
       </c>
       <c r="L16" t="n">
-        <v>9.543999999999999</v>
+        <v>10.9497</v>
       </c>
       <c r="M16" t="n">
-        <v>-32.9038</v>
+        <v>-31.9069</v>
       </c>
       <c r="N16" t="n">
-        <v>-20.3459</v>
+        <v>-21.239</v>
       </c>
       <c r="O16" t="n">
-        <v>-12.5577</v>
+        <v>-10.6676</v>
       </c>
       <c r="P16" t="n">
-        <v>12.3068</v>
+        <v>8.399699999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-22.2689</v>
+        <v>-24.8084</v>
       </c>
       <c r="R16" t="n">
-        <v>34.5756</v>
+        <v>33.2082</v>
       </c>
       <c r="S16" t="n">
-        <v>-10.8296</v>
+        <v>-8.983499999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-7.0936</v>
+        <v>-8.1515</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.7361</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-17.2417</v>
+        <v>-6.5176</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2763</v>
+        <v>7.311599999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-18.5182</v>
+        <v>-13.8292</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>R. GUARDIOLA DISPES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>-27.2449</v>
+        <v>-26.0675</v>
       </c>
       <c r="E17" t="n">
-        <v>-23.6705</v>
+        <v>-13.3755</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.5745</v>
+        <v>-12.6919</v>
       </c>
       <c r="G17" t="n">
-        <v>-17.1592</v>
+        <v>-10.5267</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.2798</v>
+        <v>-13.4985</v>
       </c>
       <c r="I17" t="n">
-        <v>-8.8796</v>
+        <v>2.971699999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2266</v>
+        <v>8.124000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2589</v>
+        <v>-0.3865000000000005</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03249999999999997</v>
+        <v>8.5106</v>
       </c>
       <c r="M17" t="n">
-        <v>-15.9329</v>
+        <v>-18.6506</v>
       </c>
       <c r="N17" t="n">
-        <v>-7.020700000000001</v>
+        <v>-13.1119</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.912099999999999</v>
+        <v>-5.5388</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1721</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-22.8548</v>
+        <v>-23.2458</v>
       </c>
       <c r="R17" t="n">
-        <v>21.6832</v>
+        <v>21.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4577</v>
+        <v>-6.2005</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.703</v>
+        <v>-3.0185</v>
       </c>
       <c r="U17" t="n">
-        <v>4.160600000000001</v>
+        <v>-3.182</v>
       </c>
       <c r="V17" t="n">
-        <v>-11.3713</v>
+        <v>-7.7774</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1141</v>
+        <v>4.7647</v>
       </c>
       <c r="X17" t="n">
-        <v>-13.4853</v>
+        <v>-12.5421</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>-28.0092</v>
+        <v>-27.2074</v>
       </c>
       <c r="E18" t="n">
-        <v>-14.1554</v>
+        <v>-6.6248</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.8538</v>
+        <v>-20.5829</v>
       </c>
       <c r="G18" t="n">
-        <v>-15.8363</v>
+        <v>-11.4427</v>
       </c>
       <c r="H18" t="n">
-        <v>-12.5366</v>
+        <v>-8.428699999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.2995</v>
+        <v>-3.014</v>
       </c>
       <c r="J18" t="n">
-        <v>7.7692</v>
+        <v>21.4613</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8878</v>
+        <v>11.9172</v>
       </c>
       <c r="L18" t="n">
-        <v>5.8814</v>
+        <v>9.543999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-23.6053</v>
+        <v>-32.9038</v>
       </c>
       <c r="N18" t="n">
-        <v>-14.4243</v>
+        <v>-20.3459</v>
       </c>
       <c r="O18" t="n">
-        <v>-9.180899999999999</v>
+        <v>-12.5577</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.7114</v>
+        <v>12.3068</v>
       </c>
       <c r="Q18" t="n">
-        <v>-24.6133</v>
+        <v>-22.2689</v>
       </c>
       <c r="R18" t="n">
-        <v>20.9017</v>
+        <v>34.5756</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6494000000000001</v>
+        <v>-10.8296</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.8526</v>
+        <v>-7.0936</v>
       </c>
       <c r="U18" t="n">
-        <v>2.2034</v>
+        <v>-3.7361</v>
       </c>
       <c r="V18" t="n">
-        <v>-7.811999999999999</v>
+        <v>-17.2417</v>
       </c>
       <c r="W18" t="n">
-        <v>5.5416</v>
+        <v>1.2763</v>
       </c>
       <c r="X18" t="n">
-        <v>-13.3537</v>
+        <v>-18.5182</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>-56.2093</v>
+        <v>-27.2449</v>
       </c>
       <c r="E19" t="n">
-        <v>-29.7987</v>
+        <v>-23.6705</v>
       </c>
       <c r="F19" t="n">
-        <v>-26.4104</v>
+        <v>-3.5745</v>
       </c>
       <c r="G19" t="n">
-        <v>-38.9941</v>
+        <v>-17.1592</v>
       </c>
       <c r="H19" t="n">
-        <v>-22.4633</v>
+        <v>-8.2798</v>
       </c>
       <c r="I19" t="n">
-        <v>-16.5307</v>
+        <v>-8.8796</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.5686</v>
+        <v>-1.2266</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.8868</v>
+        <v>-1.2589</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.681700000000001</v>
+        <v>0.03249999999999997</v>
       </c>
       <c r="M19" t="n">
-        <v>-32.4257</v>
+        <v>-15.9329</v>
       </c>
       <c r="N19" t="n">
-        <v>-17.5768</v>
+        <v>-7.020700000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-14.849</v>
+        <v>-8.912099999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.1485</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-31.8408</v>
+        <v>-22.8548</v>
       </c>
       <c r="R19" t="n">
-        <v>29.6924</v>
+        <v>21.6832</v>
       </c>
       <c r="S19" t="n">
-        <v>-11.0464</v>
+        <v>2.4577</v>
       </c>
       <c r="T19" t="n">
-        <v>-7.6792</v>
+        <v>-1.703</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.3669</v>
+        <v>4.160600000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-4.020299999999999</v>
+        <v>-11.3713</v>
       </c>
       <c r="W19" t="n">
-        <v>16.2899</v>
+        <v>2.1141</v>
       </c>
       <c r="X19" t="n">
-        <v>-20.3102</v>
+        <v>-13.4853</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,147 +1966,303 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>-65.2516</v>
+        <v>-28.0092</v>
       </c>
       <c r="E20" t="n">
-        <v>-42.4715</v>
+        <v>-14.1554</v>
       </c>
       <c r="F20" t="n">
-        <v>-22.7803</v>
+        <v>-13.8538</v>
       </c>
       <c r="G20" t="n">
-        <v>-45.7031</v>
+        <v>-15.8363</v>
       </c>
       <c r="H20" t="n">
-        <v>-21.2783</v>
+        <v>-12.5366</v>
       </c>
       <c r="I20" t="n">
-        <v>-24.4247</v>
+        <v>-3.2995</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.774</v>
+        <v>7.7692</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.2527</v>
+        <v>1.8878</v>
       </c>
       <c r="L20" t="n">
-        <v>-10.5212</v>
+        <v>5.8814</v>
       </c>
       <c r="M20" t="n">
-        <v>-32.929</v>
+        <v>-23.6053</v>
       </c>
       <c r="N20" t="n">
-        <v>-19.0256</v>
+        <v>-14.4243</v>
       </c>
       <c r="O20" t="n">
-        <v>-13.9039</v>
+        <v>-9.180899999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-8.7903</v>
+        <v>-3.7114</v>
       </c>
       <c r="Q20" t="n">
-        <v>-35.1615</v>
+        <v>-24.6133</v>
       </c>
       <c r="R20" t="n">
-        <v>26.3712</v>
+        <v>20.9017</v>
       </c>
       <c r="S20" t="n">
-        <v>-12.7529</v>
+        <v>-0.6494000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-7.7792</v>
+        <v>-2.8526</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.9735</v>
+        <v>2.2034</v>
       </c>
       <c r="V20" t="n">
-        <v>1.9949</v>
+        <v>-7.811999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>13.2431</v>
+        <v>5.5416</v>
       </c>
       <c r="X20" t="n">
-        <v>-11.2482</v>
+        <v>-13.3537</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>J. CALLAVE FERRER</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>24</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-56.2093</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-29.7987</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-26.4104</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-38.9941</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-22.4633</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-16.5307</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-6.5686</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-4.8868</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-1.681700000000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-32.4257</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-17.5768</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-14.849</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-2.1485</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-31.8408</v>
+      </c>
+      <c r="R21" t="n">
+        <v>29.6924</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-11.0464</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-7.6792</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-3.3669</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-4.020299999999999</v>
+      </c>
+      <c r="W21" t="n">
+        <v>16.2899</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-20.3102</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>M. MONTSERRAT SERRA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-65.2516</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-42.4715</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-22.7803</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-45.7031</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-21.2783</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-24.4247</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-12.774</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-2.2527</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-10.5212</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-32.929</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-19.0256</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-13.9039</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-8.7903</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-35.1615</v>
+      </c>
+      <c r="R22" t="n">
+        <v>26.3712</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-12.7529</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-7.7792</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-4.9735</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.9949</v>
+      </c>
+      <c r="W22" t="n">
+        <v>13.2431</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-11.2482</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>CB QUART GRUES CRUZ</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C23" t="n">
         <v>26</v>
       </c>
-      <c r="D21" t="n">
-        <v>-333.1088</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-151.3826</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="D23" t="n">
+        <v>-333.1089</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-151.3827</v>
+      </c>
+      <c r="F23" t="n">
         <v>-181.7264</v>
       </c>
-      <c r="G21" t="n">
-        <v>-182.5437</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-153.5501</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-28.99270000000001</v>
-      </c>
-      <c r="J21" t="n">
-        <v>154.0324</v>
-      </c>
-      <c r="K21" t="n">
-        <v>62.15320000000001</v>
-      </c>
-      <c r="L21" t="n">
-        <v>91.87889999999999</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="G23" t="n">
+        <v>-182.5438</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-153.55</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-28.9927</v>
+      </c>
+      <c r="J23" t="n">
+        <v>154.0323</v>
+      </c>
+      <c r="K23" t="n">
+        <v>62.15330000000001</v>
+      </c>
+      <c r="L23" t="n">
+        <v>91.87899999999999</v>
+      </c>
+      <c r="M23" t="n">
         <v>-336.5766</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N23" t="n">
         <v>-215.704</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O23" t="n">
         <v>-120.8723</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P23" t="n">
         <v>-2.929700000000004</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q23" t="n">
         <v>-364.3126</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R23" t="n">
         <v>361.3839</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S23" t="n">
         <v>-98.771</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T23" t="n">
         <v>-82.6189</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U23" t="n">
         <v>-16.1515</v>
       </c>
-      <c r="V21" t="n">
-        <v>-48.86339999999999</v>
-      </c>
-      <c r="W21" t="n">
+      <c r="V23" t="n">
+        <v>-48.8634</v>
+      </c>
+      <c r="W23" t="n">
         <v>141.5172</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X23" t="n">
         <v>-190.3805</v>
       </c>
     </row>
